--- a/tools/SitesOfGrace_Saints_EXPANSION_2026-09.xlsx
+++ b/tools/SitesOfGrace_Saints_EXPANSION_2026-09.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saints" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Existing_Date_Updates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Site_Saint_Links" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Existing_Review" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Saints" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Existing_Date_Updates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Site_Saint_Links" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Existing_Review" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Saints'!$A$1:$Q$291</definedName>
@@ -506,17 +506,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Built 2 September 2026. Expands the saints table from 210 to 500 records.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -526,28 +526,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   python manage.py import_catalog SitesOfGrace_Saints_EXPANSION_2026-09.xlsx --only saints --dry-run</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Check the counts, then run it again without --dry-run.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   The 'Saints' tab holds ONLY new records. Nothing in it touches an existing page.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -595,14 +595,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   See the 'Existing_Date_Updates' tab. Run patch-saint-dates.bat.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
+      <c r="A18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -612,28 +612,28 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   See the 'Site_Saint_Links' tab. The associated_saint_proposed column fills 56 of the</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   88 blank site links using the existing single-saint field -- no schema change needed.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   The related_saints_proposed column needs the new many-to-many field first (Phase 2).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
+      <c r="A23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -643,14 +643,14 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Duplicates and non-person entries. These need a decision, not an import.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -660,35 +660,35 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   significance -- one or two sentences; this is the card text in the saints directory</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   patronage    -- comma separated</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   body_draft   -- the narrative; plain text is wrapped in &lt;p&gt; automatically</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   portrait_filename, topics -- optional</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
+      <c r="A32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
+      <c r="A38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -736,49 +736,49 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Feast days and ranks: current General Roman Calendar and the USCCB proper calendar</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">      for the dioceses of the United States.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Canonization dates: per-pontificate canonization records, 1903 to September 2026,</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">      cross-checked against Vatican records where they were reachable.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Every row carries its own source_note. Facts only -- no narrative text was copied</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">      from any source, so there is nothing here with a licence attached.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
+      <c r="A46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
+      <c r="A51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -2786,8 +2786,19 @@
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr"/>
-      <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr"/>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>Peasant girl who saw the Virgin Mary eighteen times at Lourdes in 1858; the spring she uncovered still draws pilgrims seeking healing.</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>Bernadette Soubirous was born in 1844 to a desperately poor milling family in Lourdes, in the French Pyrenees. In February 1858, fourteen-year-old Bernadette was gathering firewood near the Grotto of Massabielle when a beautiful lady appeared to her in a niche in the rock. Over the following months the lady appeared seventeen more times, eventually identifying herself with words Bernadette did not understand until a priest explained them: “I am the Immaculate Conception.”
+During one apparition Bernadette was told to dig in the dry ground of the grotto; a spring welled up that continues to flow today, and reports of healing at the water began almost immediately. Bernadette herself sought no attention from the fame that followed. Civil and church authorities interrogated her repeatedly, and she answered every question the same simple way, never adding or embellishing.
+In 1866 she entered the Sisters of Charity at Nevers, far from the crowds at Lourdes, and lived the rest of her short life in humble convent work, often in poor health. She died in 1879 at thirty-five.
+Her body was found incorrupt when it was exhumed decades later and can still be seen today in a glass reliquary at the Convent of Saint-Gildard in Nevers, while Lourdes itself has become one of the world’s great pilgrimage destinations for the sick and suffering.</t>
+        </is>
+      </c>
       <c r="L35" s="7" t="inlineStr"/>
       <c r="M35" s="9" t="inlineStr">
         <is>
@@ -3281,8 +3292,19 @@
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr"/>
-      <c r="J44" s="8" t="inlineStr"/>
-      <c r="K44" s="8" t="inlineStr"/>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>Teenage computer programmer who catalogued Eucharistic miracles online before dying at fifteen; the Church’s first millennial saint.</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>Carlo Acutis was born in London in 1991 to Italian parents and grew up in Milan, an ordinary boy who loved video games, dogs, and his PlayStation. From childhood, though, he had an extraordinary devotion to the Eucharist, attending daily Mass and calling it his “highway to heaven.”
+As a teenager he taught himself computer programming and built a website documenting Eucharistic miracles recognized by the Church across the centuries, hoping to make the faith more visible to people his own age. Classmates remembered him as cheerful and unpretentious, quick to defend anyone being bullied and generous with his allowance toward the homeless near his school.
+In 2006 he was diagnosed with an aggressive form of leukemia. He offered his suffering for the Pope and for the Church and died within days, at fifteen. He had asked to be buried in Assisi, a city whose poverty and simplicity he loved.
+He rests today in the Sanctuary of the Spoliation in Assisi, dressed as he asked in jeans, sneakers, and a zip-up jacket rather than formal vestments. Beatified in 2020 and canonized in 2025, he is venerated as the first saint of the millennial generation, and young pilgrims visit his tomb in growing numbers.</t>
+        </is>
+      </c>
       <c r="L44" s="7" t="inlineStr"/>
       <c r="M44" s="9" t="inlineStr">
         <is>
@@ -3501,8 +3523,19 @@
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr"/>
-      <c r="J48" s="8" t="inlineStr"/>
-      <c r="K48" s="8" t="inlineStr"/>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>French religious sister who received the Virgin Mary’s instructions for the Miraculous Medal in a Paris convent chapel in 1830.</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>Catherine Labouré was born to a farming family in Burgundy in 1806 and entered the Daughters of Charity in Paris as a young woman, largely unnoticed among her novice companions. In the chapel of the community’s motherhouse on the Rue du Bac, over several months in 1830, she experienced a series of apparitions of the Virgin Mary.
+In the most famous of these, Mary appeared framed within an oval, surrounded by words asking for prayer, and showed Catherine a design for a medal she wanted struck: an image now known as the Miraculous Medal. Catherine reported everything to her confessor but otherwise kept the visions almost entirely to herself for the rest of her life, telling no one else even as the medal she had described was struck by the millions and carried around the world.
+She spent more than forty years afterward in quiet, unglamorous work, caring for the elderly and infirm at a hospice in Paris, known to those around her simply as a humble and reliable sister rather than a visionary. Only in the last months before her death in 1876 did she reveal to her superior that she had been the recipient of the Rue du Bac apparitions.
+Her body was found incorrupt when it was exhumed, and it remains on view today in the chapel on the Rue du Bac where the apparitions took place, a place of quiet pilgrimage in the heart of Paris.</t>
+        </is>
+      </c>
       <c r="L48" s="7" t="inlineStr"/>
       <c r="M48" s="9" t="inlineStr">
         <is>
@@ -4601,8 +4634,19 @@
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr"/>
-      <c r="J68" s="8" t="inlineStr"/>
-      <c r="K68" s="8" t="inlineStr"/>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>Widowed New York socialite turned Catholic convert who founded America’s Catholic school system; the first US-born canonized saint.</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>Elizabeth Ann Seton was born in 1774 into a prominent Episcopalian family in New York City. She married a wealthy merchant, William Seton, and raised five children in comfortable society until his business failed and his health collapsed. She nursed him on a voyage to Italy hoping the climate would help, but he died there in 1803, leaving her a widow at twenty-nine.
+In Italy she encountered the Catholic faith through friends who cared for her in her grief, and after a long struggle of conscience she entered the Catholic Church in 1805, a decision that cost her much of her family’s support and society standing. She moved to Emmitsburg, Maryland, at the invitation of the local bishop and founded the Sisters of Charity of St. Joseph, the first American religious community for women.
+There she opened a free school for girls that became the model for the American Catholic parochial school system, and her sisters went on to establish orphanages and hospitals across the country. She died in 1821, having built, in less than two decades, much of the framework of Catholic education in the United States.
+She was canonized in 1975, the first person born in the United States to be declared a saint. Her shrine in Emmitsburg, built around the original convent and school, remains a place of pilgrimage.</t>
+        </is>
+      </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/General_Roman_Calendar</t>
@@ -5269,8 +5313,19 @@
         </is>
       </c>
       <c r="I80" s="8" t="inlineStr"/>
-      <c r="J80" s="8" t="inlineStr"/>
-      <c r="K80" s="8" t="inlineStr"/>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>Italian-born founder of schools, hospitals, and orphanages for immigrants; the first US citizen ever canonized.</t>
+        </is>
+      </c>
+      <c r="K80" s="8" t="inlineStr">
+        <is>
+          <t>Frances Xavier Cabrini was born in Lombardy, Italy, in 1850, the youngest of thirteen children. Repeatedly refused admission to religious orders because of poor health, she instead founded her own congregation in 1880, the Missionary Sisters of the Sacred Heart of Jesus. She had long dreamed of missionary work in China, but Pope Leo XIII redirected her instead: “Not to the East, but to the West.”
+She arrived in New York in 1889 to find Italian immigrants living in desperate poverty, distrusted by American society and unwelcome even in some parishes. Cabrini spent the rest of her life building institutions for them and for the poor generally: schools, orphanages, and hospitals, first across the United States and eventually throughout Latin America and Europe. She became a US citizen in 1909, the better to serve the country she had adopted.
+Despite a lifelong fear of drowning after a childhood accident, she crossed the Atlantic more than thirty times establishing her institutions. By her death in 1917 she had founded around seventy schools, hospitals, and orphanages on three continents.
+She was canonized in 1946, the first citizen of the United States to be declared a saint, and is honored as patroness of immigrants. Her body rests at the National Shrine of Mother Cabrini in New York, still a place where immigrant communities come to pray.</t>
+        </is>
+      </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/General_Roman_Calendar</t>
@@ -5603,8 +5658,19 @@
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr"/>
-      <c r="J86" s="8" t="inlineStr"/>
-      <c r="K86" s="8" t="inlineStr"/>
+      <c r="J86" s="8" t="inlineStr">
+        <is>
+          <t>One of the three shepherd children who saw Our Lady of Fátima in 1917; died young after quietly bearing the illness that followed.</t>
+        </is>
+      </c>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>Francisco Marto was nine years old in 1917 when he, his younger sister Jacinta, and their cousin Lúcia dos Santos began seeing apparitions of a lady “brighter than the sun” while tending sheep near their village of Fátima, Portugal. Unlike his sister and cousin, Francisco could see the lady but not hear her speak directly to him; what he knew of her words came through the other two.
+He was known among the three as the quiet one, given to long stretches of silent prayer. After the apparitions, he told his family he most wanted to “console Jesus,” who he said was saddened by the sins of the world, and he began spending hours alone in the family’s small chapel and in the fields, praying in reparation.
+In 1918 the influenza pandemic sweeping Europe reached Fátima, and Francisco fell seriously ill. He bore the long illness patiently, refusing medicine at times so that his sacrifice would be complete, and died at home in 1919, not yet eleven.
+He and Jacinta were canonized together in 2017, the youngest saints in the Church’s history who were not martyrs. Both are buried at the Basilica of Our Lady of the Rosary at Fátima, within the shrine that grew up around the fields where they once watched their sheep.</t>
+        </is>
+      </c>
       <c r="L86" s="7" t="inlineStr"/>
       <c r="M86" s="9" t="inlineStr">
         <is>
@@ -7473,8 +7539,19 @@
         </is>
       </c>
       <c r="I120" s="8" t="inlineStr"/>
-      <c r="J120" s="8" t="inlineStr"/>
-      <c r="K120" s="8" t="inlineStr"/>
+      <c r="J120" s="8" t="inlineStr">
+        <is>
+          <t>Youngest of the three Fátima visionaries, remembered for her passionate concern for sinners; canonized alongside her brother Francisco in 2017.</t>
+        </is>
+      </c>
+      <c r="K120" s="8" t="inlineStr">
+        <is>
+          <t>Jacinta Marto was seven, the youngest of the three shepherd children of Fátima, Portugal, when she began seeing apparitions of the Virgin Mary alongside her brother Francisco and their cousin Lúcia in 1917. Of the three, Jacinta spoke most freely afterward about what she had seen and heard, including a vision of hell that left a lasting mark on her.
+Where Francisco turned inward, Jacinta’s response was urgent and outward: she begged people to stop offending God, took on small penances and hidden sacrifices, and repeated often that she wanted to save souls. Those who knew her described a lively, affectionate child whose devotion had none of the somberness adults sometimes expect of visionaries.
+Like her brother, she caught influenza in the 1918 pandemic, and her illness worsened into pleurisy that required a difficult, lonely hospital stay far from her family. She died in Lisbon in 1920, at nine years old, having told those around her in advance that she would not recover.
+She and Francisco were canonized together by Pope Francis in 2017, on the hundredth anniversary of the apparitions. Both children are buried at the Basilica of Our Lady of the Rosary at Fátima, in the shrine built on the site of the apparitions they once described to a skeptical world.</t>
+        </is>
+      </c>
       <c r="L120" s="7" t="inlineStr"/>
       <c r="M120" s="9" t="inlineStr">
         <is>
@@ -10097,8 +10174,19 @@
       <c r="G168" s="7" t="inlineStr"/>
       <c r="H168" s="7" t="inlineStr"/>
       <c r="I168" s="8" t="inlineStr"/>
-      <c r="J168" s="8" t="inlineStr"/>
-      <c r="K168" s="8" t="inlineStr"/>
+      <c r="J168" s="8" t="inlineStr">
+        <is>
+          <t>The friend Jesus raised from the dead after four days in the tomb, in the most dramatic of the Gospel miracles (John 11).</t>
+        </is>
+      </c>
+      <c r="K168" s="8" t="inlineStr">
+        <is>
+          <t>Lazarus lived in Bethany, a village near Jerusalem, with his sisters Martha and Mary. The Gospel of John describes the three as close friends of Jesus, who often stayed in their home. When Lazarus fell ill, his sisters sent word to Jesus, but he delayed his arrival for two days, arriving only after Lazarus had already died and lain four days in the tomb.
+At the tomb Jesus wept, and then, before a gathered crowd, called out, “Lazarus, come out.” Lazarus emerged still bound in his burial cloths. It is the last and greatest of the miracles John records before Jesus’s own death and resurrection, and in the Gospel’s telling it becomes a direct cause of the plot against his life: the raising was so public and so undeniable that the religious authorities in Jerusalem resolved he had to be stopped.
+Later Christian tradition adds much to this spare biblical account — that Lazarus went on to become a bishop, that he never spoke of what he had seen beyond death — but none of it carries the same certainty as the Gospel scene itself. What is certain is the household at Bethany, where Jesus was known and welcomed, and the tomb from which Lazarus walked out alive.
+Pilgrims visit that tomb in Bethany today, a short climb down stone steps to the burial chamber the Gospel describes, still venerated as the site of the miracle.</t>
+        </is>
+      </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/General_Roman_Calendar</t>
